--- a/config/xlsx/game_config.xlsx
+++ b/config/xlsx/game_config.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,30 +498,50 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>reset_hour</t>
+          <t>stamina.multiplier_threshold_base</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>craft_speedup_stone_cost_per_minute</t>
+          <t>stamina.multiplier_duration</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>reset_hour</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>craft_speedup_stone_cost_per_minute</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>launcher_speedup_stone_cost_per_minute</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/config/xlsx/game_config.xlsx
+++ b/config/xlsx/game_config.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="game_config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_config" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -545,6 +545,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>battle_pass.premium_unlock_cost</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>battle_pass.points_per_value</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/xlsx/game_config.xlsx
+++ b/config/xlsx/game_config.xlsx
@@ -575,6 +575,30 @@
         <x:v>50</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>resource_purchase.base_cost</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>resource_purchase.cost_increment</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>resource_purchase.amount</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
